--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,12 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720065.4055682207</v>
+        <v>720065</v>
       </c>
       <c r="R3" t="n">
-        <v>6415853.446892135</v>
+        <v>6415853</v>
       </c>
       <c r="S3" t="n">
         <v>71</v>
@@ -874,19 +869,9 @@
           <t>1996-08-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1996-08-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720065.4055682207</v>
+        <v>720065</v>
       </c>
       <c r="R4" t="n">
-        <v>6415853.446892135</v>
+        <v>6415853</v>
       </c>
       <c r="S4" t="n">
         <v>71</v>
@@ -1001,19 +981,9 @@
           <t>1996-08-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1996-08-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98616</v>
+        <v>98622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105533</v>
+        <v>105542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105542</v>
+        <v>105554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105626</v>
+        <v>105634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>87178118</v>
       </c>
       <c r="B2" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720224.4371702594</v>
+        <v>720224</v>
       </c>
       <c r="R2" t="n">
-        <v>6415731.971262196</v>
+        <v>6415732</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -761,19 +756,9 @@
           <t>2020-07-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,7 +789,7 @@
         <v>106593744</v>
       </c>
       <c r="B3" t="n">
-        <v>98696</v>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +901,7 @@
         <v>106593743</v>
       </c>
       <c r="B4" t="n">
-        <v>105634</v>
+        <v>106156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53552-2021 artfynd.xlsx
+++ b/artfynd/A 53552-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87178118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106593744</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,8 +1022,18 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106593743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>